--- a/For SY.xlsx
+++ b/For SY.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bek C\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seyoung/Documents/MATLAB/EAF_modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938D43CD-4D05-4E56-80AB-AAC4B5ECDBEB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3758C6DC-D02B-594A-965D-6B71B8D6C5C8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{2D61319A-36D5-4AE1-883B-AA4521FCAFF7}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{2D61319A-36D5-4AE1-883B-AA4521FCAFF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -486,13 +495,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{121F202C-5F6D-4317-A5E8-2F2958252E8F}">
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>29</v>
       </c>
@@ -500,7 +509,7 @@
         <v>1213.2220168925201</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -508,15 +517,19 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2">
         <v>345233.616062421</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="C3">
+        <f>(B14+B16+B17+B22+B25+B26+B29+B30)</f>
+        <v>344911.89824621036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -524,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -532,7 +545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -540,7 +553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -548,7 +561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -556,7 +569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -564,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -572,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -580,7 +593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -588,7 +601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -596,7 +609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -604,7 +617,7 @@
         <v>308662.5102930807</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -612,7 +625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
@@ -620,7 +633,7 @@
         <v>2024.2905132533904</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -628,7 +641,7 @@
         <v>19870.805810485799</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -636,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -644,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -652,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>18</v>
       </c>
@@ -660,7 +673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
@@ -668,7 +681,7 @@
         <v>12916.023776827264</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -676,7 +689,7 @@
         <v>23.655721202973432</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>21</v>
       </c>
@@ -684,7 +697,7 @@
         <v>61.504875127713518</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>22</v>
       </c>
@@ -692,7 +705,7 @@
         <v>473.11442405907712</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>23</v>
       </c>
@@ -700,7 +713,7 @@
         <v>283.86865443534549</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>24</v>
       </c>
@@ -708,7 +721,7 @@
         <v>160.85890418014114</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>25</v>
       </c>
@@ -716,7 +729,7 @@
         <v>75.698315699789632</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
@@ -724,7 +737,7 @@
         <v>33.118013119004985</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>27</v>
       </c>
@@ -732,7 +745,7 @@
         <v>648.16676094983063</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
@@ -746,21 +759,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010058E8B55A6D7FB24794DCC589E6B728F0" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6031f07320a892abf0f536dce71b90f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4d921238-894a-41fb-8d98-ce6b61ed10f5" xmlns:ns4="38531080-8ac3-43ce-9ba8-1a9673c1b68f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d0e464e4d4e9c2b93bd9266b9dda2f1" ns3:_="" ns4:_="">
     <xsd:import namespace="4d921238-894a-41fb-8d98-ce6b61ed10f5"/>
@@ -977,32 +975,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3763A13-FC34-4DC6-AB62-CECE2DC51446}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="38531080-8ac3-43ce-9ba8-1a9673c1b68f"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4d921238-894a-41fb-8d98-ce6b61ed10f5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B2AF97F-FF59-4D29-BF91-8E385978D432}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C91191-823A-4A7A-AA20-C9708A37DD1C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1019,4 +1007,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B2AF97F-FF59-4D29-BF91-8E385978D432}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3763A13-FC34-4DC6-AB62-CECE2DC51446}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="38531080-8ac3-43ce-9ba8-1a9673c1b68f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4d921238-894a-41fb-8d98-ce6b61ed10f5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>